--- a/TP6/example-linear-regression.xlsx
+++ b/TP6/example-linear-regression.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anparis\Documents\LBIR1251\lbir1251-data-analysis\TP6\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anparis\Documents\LBIR1251\lbir1251-public-data\TP6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA0B1E47-34A0-41DB-B7A1-22F2B765231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DE38A6-DA36-4B2A-B170-1190BA8B1873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE0503B6-221A-40D0-96B5-17E07C1F3186}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -473,11 +473,11 @@
       </c>
       <c r="B2">
         <f ca="1" xml:space="preserve"> 67 + 1.42 * A2 + + NORMINV(RAND(), 0, 2.5)</f>
-        <v>66.120729108612565</v>
+        <v>68.938756112412406</v>
       </c>
       <c r="C2">
-        <f ca="1" xml:space="preserve"> 42 + 0.67 * A2 + NORMINV(RAND(), 0, 4)</f>
-        <v>40.723320346753304</v>
+        <f ca="1" xml:space="preserve"> 42 + 8.67 * A2 + NORMINV(RAND(), 0, 4)</f>
+        <v>45.341359273670022</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -486,11 +486,11 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B66" ca="1" si="0" xml:space="preserve"> 67 + 1.42 * A3 + NORMINV(RAND(), 0, 2.5)</f>
-        <v>66.596778741935907</v>
+        <v>68.20297751355757</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C66" ca="1" si="1" xml:space="preserve"> 42 + 0.67 * A3 + NORMINV(RAND(), 0, 4)</f>
-        <v>39.001740008554243</v>
+        <f t="shared" ref="C3:C66" ca="1" si="1" xml:space="preserve"> 42 + 8.67 * A3 + NORMINV(RAND(), 0, 4)</f>
+        <v>32.564366094575334</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -499,11 +499,11 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="0"/>
-        <v>66.713404219164389</v>
+        <v>69.071903329890617</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="1"/>
-        <v>42.523671296581441</v>
+        <v>45.399224185599472</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -512,11 +512,11 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>66.783414254873961</v>
+        <v>66.892156616823769</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="1"/>
-        <v>49.638465190781794</v>
+        <v>47.783724559839492</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -525,11 +525,11 @@
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="0"/>
-        <v>68.159476347318133</v>
+        <v>71.375908848229074</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="1"/>
-        <v>40.722401571555416</v>
+        <v>49.687616236735586</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -538,11 +538,11 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="0"/>
-        <v>65.691289142691744</v>
+        <v>67.419272912246001</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="1"/>
-        <v>43.488425959157965</v>
+        <v>48.609923734941582</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -551,11 +551,11 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="0"/>
-        <v>71.441916638950474</v>
+        <v>67.024845368807021</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>42.355439070940463</v>
+        <v>46.330148184809254</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,11 +564,11 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="0"/>
-        <v>64.586573498788496</v>
+        <v>71.152305620486501</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>39.187403613496045</v>
+        <v>49.740408608124248</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,11 +577,11 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="0"/>
-        <v>67.496348144551163</v>
+        <v>67.355888353216073</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>38.030343742192521</v>
+        <v>39.063060131610179</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -590,11 +590,11 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="0"/>
-        <v>67.620641083272233</v>
+        <v>64.555741077717144</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>42.358323402900012</v>
+        <v>42.413661747247559</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="0"/>
-        <v>66.05706099299654</v>
+        <v>67.979550067555834</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>46.169283379660243</v>
+        <v>46.221315586283481</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -616,11 +616,11 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="0"/>
-        <v>67.518987785408868</v>
+        <v>69.767263964360708</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>38.399289079891552</v>
+        <v>50.64483316794162</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,11 +629,11 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.109294711546482</v>
+        <v>69.048488758560111</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>45.822584289817456</v>
+        <v>55.291226052864602</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -642,11 +642,11 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="0"/>
-        <v>67.774444222292161</v>
+        <v>67.2307340300639</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>52.507096697232413</v>
+        <v>61.630802088589235</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -655,11 +655,11 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="0"/>
-        <v>64.48394721737256</v>
+        <v>68.706052427173319</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>46.613011171778126</v>
+        <v>52.754708356057243</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -668,11 +668,11 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="0"/>
-        <v>71.445424843651125</v>
+        <v>65.474710329309644</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>41.273858788604414</v>
+        <v>57.9608583309331</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -681,11 +681,11 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="0"/>
-        <v>70.189594718953515</v>
+        <v>70.433128107370337</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>39.582356402737581</v>
+        <v>52.901009351930135</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,11 +694,11 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="0"/>
-        <v>69.236788249710287</v>
+        <v>70.744086427531869</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>40.533084084292412</v>
+        <v>54.243413901808069</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,11 +707,11 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="0"/>
-        <v>70.291056244465409</v>
+        <v>72.372577979595775</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>41.663648447556746</v>
+        <v>61.772189764613621</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,11 +720,11 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="0"/>
-        <v>66.779475312167023</v>
+        <v>69.009383805920464</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>37.657298203637467</v>
+        <v>59.320985875738494</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -733,11 +733,11 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="0"/>
-        <v>70.050933557642196</v>
+        <v>71.590890434846486</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>38.319963479490809</v>
+        <v>55.776295667426965</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,11 +746,11 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="0"/>
-        <v>70.841105288835706</v>
+        <v>70.519466208501413</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>38.687855625251416</v>
+        <v>52.475100979373188</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -759,11 +759,11 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="0"/>
-        <v>71.442808184256492</v>
+        <v>70.893732846745635</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>38.700289715108468</v>
+        <v>58.203528730823649</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -772,11 +772,11 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="0"/>
-        <v>73.90166232574623</v>
+        <v>72.436905583448578</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="1"/>
-        <v>40.575539496359923</v>
+        <v>60.455958963336897</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -785,11 +785,11 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="0"/>
-        <v>67.395820777861758</v>
+        <v>68.681331604485223</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="1"/>
-        <v>44.804742191987756</v>
+        <v>59.637792776178934</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="0"/>
-        <v>70.719180479677092</v>
+        <v>70.625226160767241</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="1"/>
-        <v>48.021210699414745</v>
+        <v>62.616117505458377</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -811,11 +811,11 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="0"/>
-        <v>73.888225326611519</v>
+        <v>70.261279361829239</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="1"/>
-        <v>42.552911741391213</v>
+        <v>64.205269800707825</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,11 +824,11 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="0"/>
-        <v>70.718476815460392</v>
+        <v>70.023894358719133</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="1"/>
-        <v>50.334281978407432</v>
+        <v>67.019598933805497</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,11 +837,11 @@
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="0"/>
-        <v>70.266670897692208</v>
+        <v>69.668334819617726</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="1"/>
-        <v>45.294445068407974</v>
+        <v>66.082378953478425</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,11 +850,11 @@
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="0"/>
-        <v>74.618811000825104</v>
+        <v>69.403690288132154</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="1"/>
-        <v>44.446080224397456</v>
+        <v>70.040227854862209</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,11 +863,11 @@
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="0"/>
-        <v>71.267804512144025</v>
+        <v>78.918288448474073</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="1"/>
-        <v>45.920090657875562</v>
+        <v>71.211959130319258</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -876,11 +876,11 @@
       </c>
       <c r="B33">
         <f t="shared" ca="1" si="0"/>
-        <v>71.362681562716844</v>
+        <v>72.900356891210677</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="1"/>
-        <v>45.408717433134179</v>
+        <v>64.957210217294474</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -889,11 +889,11 @@
       </c>
       <c r="B34">
         <f t="shared" ca="1" si="0"/>
-        <v>69.988694092460236</v>
+        <v>70.080879281583009</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="1"/>
-        <v>43.802915919221959</v>
+        <v>74.327611362861902</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -902,11 +902,11 @@
       </c>
       <c r="B35">
         <f t="shared" ca="1" si="0"/>
-        <v>68.898989262979796</v>
+        <v>71.95190513096847</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="1"/>
-        <v>40.581667728499298</v>
+        <v>67.127443321952384</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -915,11 +915,11 @@
       </c>
       <c r="B36">
         <f t="shared" ca="1" si="0"/>
-        <v>71.718868228011502</v>
+        <v>65.823449258249326</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="1"/>
-        <v>47.666631474880703</v>
+        <v>71.776915175591043</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -928,11 +928,11 @@
       </c>
       <c r="B37">
         <f t="shared" ca="1" si="0"/>
-        <v>72.981463060367815</v>
+        <v>73.819557329335282</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="1"/>
-        <v>39.842583962116791</v>
+        <v>63.517038866529816</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -941,11 +941,11 @@
       </c>
       <c r="B38">
         <f t="shared" ca="1" si="0"/>
-        <v>70.99981184489377</v>
+        <v>75.752902116324435</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="1"/>
-        <v>41.342463959454875</v>
+        <v>75.668723253179351</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,11 +954,11 @@
       </c>
       <c r="B39">
         <f t="shared" ca="1" si="0"/>
-        <v>71.536136100019405</v>
+        <v>73.966025700591715</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="1"/>
-        <v>39.175608074287659</v>
+        <v>71.849956328101982</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -967,11 +967,11 @@
       </c>
       <c r="B40">
         <f t="shared" ca="1" si="0"/>
-        <v>73.786990958057388</v>
+        <v>72.868470330022177</v>
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="1"/>
-        <v>45.582910093770906</v>
+        <v>69.495403296982843</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,11 +980,11 @@
       </c>
       <c r="B41">
         <f t="shared" ca="1" si="0"/>
-        <v>74.494618111189155</v>
+        <v>67.781919114302198</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="1"/>
-        <v>42.566850627781143</v>
+        <v>82.04779740872732</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,11 +993,11 @@
       </c>
       <c r="B42">
         <f t="shared" ca="1" si="0"/>
-        <v>70.315850631938645</v>
+        <v>71.845010590902277</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="1"/>
-        <v>42.539746244149974</v>
+        <v>73.805370344924384</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="B43">
         <f t="shared" ca="1" si="0"/>
-        <v>70.03582352446638</v>
+        <v>71.028613812970264</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="1"/>
-        <v>48.946680935497106</v>
+        <v>69.680128048768481</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="B44">
         <f t="shared" ca="1" si="0"/>
-        <v>71.399640298743009</v>
+        <v>71.805468664964494</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="1"/>
-        <v>45.32881388339483</v>
+        <v>80.604720312695875</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="B45">
         <f t="shared" ca="1" si="0"/>
-        <v>71.427879574661873</v>
+        <v>70.555260416534992</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="1"/>
-        <v>47.182705881012872</v>
+        <v>85.943863818506529</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1045,11 +1045,11 @@
       </c>
       <c r="B46">
         <f t="shared" ca="1" si="0"/>
-        <v>76.822889410443182</v>
+        <v>73.681253808044005</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="1"/>
-        <v>42.20225567363768</v>
+        <v>81.081006971251455</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="B47">
         <f t="shared" ca="1" si="0"/>
-        <v>72.86123801719431</v>
+        <v>72.920986662639095</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="1"/>
-        <v>43.065090462565657</v>
+        <v>81.42795492695943</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="B48">
         <f t="shared" ca="1" si="0"/>
-        <v>74.548286382751883</v>
+        <v>73.550293692623427</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="1"/>
-        <v>38.701125470491164</v>
+        <v>87.137359809493148</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="B49">
         <f t="shared" ca="1" si="0"/>
-        <v>73.631930490476336</v>
+        <v>77.171858114306602</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="1"/>
-        <v>45.518041063679384</v>
+        <v>83.380021768261585</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="B50">
         <f t="shared" ca="1" si="0"/>
-        <v>69.002917289045911</v>
+        <v>69.445329017178636</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="1"/>
-        <v>43.32893314034105</v>
+        <v>85.387404780166676</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1110,11 +1110,11 @@
       </c>
       <c r="B51">
         <f t="shared" ca="1" si="0"/>
-        <v>72.956576237399332</v>
+        <v>72.826840539283069</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="1"/>
-        <v>57.451528448872622</v>
+        <v>86.996774360208875</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B52">
         <f t="shared" ca="1" si="0"/>
-        <v>74.523273744348245</v>
+        <v>74.463121485994975</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="1"/>
-        <v>48.396597353643671</v>
+        <v>80.343862210645241</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,11 +1136,11 @@
       </c>
       <c r="B53">
         <f t="shared" ca="1" si="0"/>
-        <v>74.938510744675412</v>
+        <v>73.496705129767463</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="1"/>
-        <v>39.68042959386748</v>
+        <v>83.534203332220386</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="B54">
         <f t="shared" ca="1" si="0"/>
-        <v>72.895216039827645</v>
+        <v>76.847581058239101</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="1"/>
-        <v>41.598346871849131</v>
+        <v>86.186470224011472</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1162,11 +1162,11 @@
       </c>
       <c r="B55">
         <f t="shared" ca="1" si="0"/>
-        <v>74.606387186343028</v>
+        <v>75.463266826345702</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="1"/>
-        <v>50.928212663995332</v>
+        <v>85.138826232516124</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="B56">
         <f t="shared" ca="1" si="0"/>
-        <v>71.376320406402684</v>
+        <v>74.891495880069101</v>
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="1"/>
-        <v>44.484664767057403</v>
+        <v>84.219305705688114</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B57">
         <f t="shared" ca="1" si="0"/>
-        <v>73.199901520435176</v>
+        <v>83.626772721456234</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="1"/>
-        <v>42.473519872410264</v>
+        <v>85.112348121041094</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1201,11 +1201,11 @@
       </c>
       <c r="B58">
         <f t="shared" ca="1" si="0"/>
-        <v>75.834357346730101</v>
+        <v>72.200372335213203</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="1"/>
-        <v>41.335875481389287</v>
+        <v>89.627250142421431</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1214,11 +1214,11 @@
       </c>
       <c r="B59">
         <f t="shared" ca="1" si="0"/>
-        <v>73.261189801905275</v>
+        <v>76.970008964493175</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="1"/>
-        <v>43.346329533827401</v>
+        <v>88.343166935465931</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1227,11 +1227,11 @@
       </c>
       <c r="B60">
         <f t="shared" ca="1" si="0"/>
-        <v>71.477255988642852</v>
+        <v>77.550553086240399</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="1"/>
-        <v>45.771375164737357</v>
+        <v>89.845549793340012</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1240,11 +1240,11 @@
       </c>
       <c r="B61">
         <f t="shared" ca="1" si="0"/>
-        <v>79.199633697516688</v>
+        <v>76.640429953677057</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="1"/>
-        <v>55.378916750424111</v>
+        <v>86.20782028414088</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1253,11 +1253,11 @@
       </c>
       <c r="B62">
         <f t="shared" ca="1" si="0"/>
-        <v>77.057048286752092</v>
+        <v>72.024057511200724</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="1"/>
-        <v>47.856177843014081</v>
+        <v>94.928112696791558</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="B63">
         <f t="shared" ca="1" si="0"/>
-        <v>74.482052990685176</v>
+        <v>74.262267400721896</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="1"/>
-        <v>44.867331256150621</v>
+        <v>96.646735062235464</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1279,11 +1279,11 @@
       </c>
       <c r="B64">
         <f t="shared" ca="1" si="0"/>
-        <v>72.029149421889485</v>
+        <v>76.134585901992267</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="1"/>
-        <v>47.737556685639419</v>
+        <v>94.117599598110743</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1292,11 +1292,11 @@
       </c>
       <c r="B65">
         <f t="shared" ca="1" si="0"/>
-        <v>76.288424542523927</v>
+        <v>79.644134776891249</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="1"/>
-        <v>49.5359795167698</v>
+        <v>102.64329390152091</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1305,11 +1305,11 @@
       </c>
       <c r="B66">
         <f t="shared" ca="1" si="0"/>
-        <v>74.266086975510063</v>
+        <v>75.121607402635632</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="1"/>
-        <v>46.626353996511526</v>
+        <v>93.270983566062895</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1318,11 +1318,11 @@
       </c>
       <c r="B67">
         <f t="shared" ref="B67:B101" ca="1" si="2" xml:space="preserve"> 67 + 1.42 * A67 + NORMINV(RAND(), 0, 2.5)</f>
-        <v>72.728124697190779</v>
+        <v>74.646361021448357</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C101" ca="1" si="3" xml:space="preserve"> 42 + 0.67 * A67 + NORMINV(RAND(), 0, 4)</f>
-        <v>45.20190307283422</v>
+        <f t="shared" ref="C67:C101" ca="1" si="3" xml:space="preserve"> 42 + 8.67 * A67 + NORMINV(RAND(), 0, 4)</f>
+        <v>95.673068500203343</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B68">
         <f t="shared" ca="1" si="2"/>
-        <v>80.823375963287461</v>
+        <v>72.953550371280727</v>
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="3"/>
-        <v>45.912201067322336</v>
+        <v>96.920012208872635</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="B69">
         <f t="shared" ca="1" si="2"/>
-        <v>74.727296765251538</v>
+        <v>77.246229059118491</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="3"/>
-        <v>44.780591496387082</v>
+        <v>97.370989822793135</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,11 +1357,11 @@
       </c>
       <c r="B70">
         <f t="shared" ca="1" si="2"/>
-        <v>78.890610698193299</v>
+        <v>73.722477624865363</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="3"/>
-        <v>51.166493573067669</v>
+        <v>92.708123856626528</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1370,11 +1370,11 @@
       </c>
       <c r="B71">
         <f t="shared" ca="1" si="2"/>
-        <v>76.353106045337555</v>
+        <v>77.724039334934105</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="3"/>
-        <v>49.437162751503145</v>
+        <v>97.04572104974649</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B72">
         <f t="shared" ca="1" si="2"/>
-        <v>77.12257854523925</v>
+        <v>80.134292980654465</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="3"/>
-        <v>48.007546242448171</v>
+        <v>102.97110011121512</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1396,11 +1396,11 @@
       </c>
       <c r="B73">
         <f t="shared" ca="1" si="2"/>
-        <v>71.825364690417103</v>
+        <v>77.913684661812567</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="3"/>
-        <v>36.20355179436789</v>
+        <v>103.53191825866608</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1409,11 +1409,11 @@
       </c>
       <c r="B74">
         <f t="shared" ca="1" si="2"/>
-        <v>77.840349223747921</v>
+        <v>72.37631767992697</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="3"/>
-        <v>34.389621218386502</v>
+        <v>101.62286060669946</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,11 +1422,11 @@
       </c>
       <c r="B75">
         <f t="shared" ca="1" si="2"/>
-        <v>77.819822545561877</v>
+        <v>75.321736265805612</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="3"/>
-        <v>37.382791931265601</v>
+        <v>103.50773148777556</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1435,11 +1435,11 @@
       </c>
       <c r="B76">
         <f t="shared" ca="1" si="2"/>
-        <v>76.890138630986172</v>
+        <v>74.44689471589588</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="3"/>
-        <v>50.287136504675452</v>
+        <v>102.42034535531602</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="B77">
         <f t="shared" ca="1" si="2"/>
-        <v>76.90103758386158</v>
+        <v>72.132316580372247</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="3"/>
-        <v>46.441426623325547</v>
+        <v>104.51259943073957</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1461,11 +1461,11 @@
       </c>
       <c r="B78">
         <f t="shared" ca="1" si="2"/>
-        <v>72.742824624495881</v>
+        <v>77.294257824983632</v>
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="3"/>
-        <v>48.447080907590696</v>
+        <v>103.33051087235526</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1474,11 +1474,11 @@
       </c>
       <c r="B79">
         <f t="shared" ca="1" si="2"/>
-        <v>79.387808230480658</v>
+        <v>76.65581842403725</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="3"/>
-        <v>43.486208915133027</v>
+        <v>101.68582192943178</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1487,11 +1487,11 @@
       </c>
       <c r="B80">
         <f t="shared" ca="1" si="2"/>
-        <v>75.193604564552416</v>
+        <v>76.510079230295105</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="3"/>
-        <v>42.810353300502975</v>
+        <v>116.37177746868457</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="B81">
         <f t="shared" ca="1" si="2"/>
-        <v>78.178745022165785</v>
+        <v>77.127639900191483</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="3"/>
-        <v>47.632654709594284</v>
+        <v>109.37419077663465</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1513,11 +1513,11 @@
       </c>
       <c r="B82">
         <f t="shared" ca="1" si="2"/>
-        <v>84.149473107293787</v>
+        <v>77.671079658066688</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="3"/>
-        <v>43.128078632654152</v>
+        <v>113.79638171581017</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1526,11 +1526,11 @@
       </c>
       <c r="B83">
         <f t="shared" ca="1" si="2"/>
-        <v>78.560181204658747</v>
+        <v>77.641102080912688</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="3"/>
-        <v>43.456362460687004</v>
+        <v>111.91845182185085</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B84">
         <f t="shared" ca="1" si="2"/>
-        <v>80.054863723063761</v>
+        <v>77.785624197350856</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="3"/>
-        <v>47.577085961772056</v>
+        <v>113.68941718596736</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="B85">
         <f t="shared" ca="1" si="2"/>
-        <v>72.626629968541138</v>
+        <v>81.117192878816525</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="3"/>
-        <v>45.368951663160118</v>
+        <v>115.46691328670816</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="B86">
         <f t="shared" ca="1" si="2"/>
-        <v>79.123285822699074</v>
+        <v>79.099420929086165</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="3"/>
-        <v>51.207341248226761</v>
+        <v>115.80605757271363</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="B87">
         <f t="shared" ca="1" si="2"/>
-        <v>79.290789216161144</v>
+        <v>82.573075691825409</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="3"/>
-        <v>50.358188932149098</v>
+        <v>122.20045732281963</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1591,11 +1591,11 @@
       </c>
       <c r="B88">
         <f t="shared" ca="1" si="2"/>
-        <v>81.100383783251175</v>
+        <v>77.247793235958753</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="3"/>
-        <v>51.703658769391751</v>
+        <v>122.23308454189021</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1604,11 +1604,11 @@
       </c>
       <c r="B89">
         <f t="shared" ca="1" si="2"/>
-        <v>77.588807547447686</v>
+        <v>81.824293309587205</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="3"/>
-        <v>50.009398615346953</v>
+        <v>115.44420133533487</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="B90">
         <f t="shared" ca="1" si="2"/>
-        <v>84.941088938117403</v>
+        <v>77.034857768460142</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="3"/>
-        <v>44.839983629596425</v>
+        <v>115.31998657646466</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1630,11 +1630,11 @@
       </c>
       <c r="B91">
         <f t="shared" ca="1" si="2"/>
-        <v>78.951567983362267</v>
+        <v>80.33418051608048</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="3"/>
-        <v>46.544940270478733</v>
+        <v>111.66849696691894</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="B92">
         <f t="shared" ca="1" si="2"/>
-        <v>82.22205384749924</v>
+        <v>80.464001732445865</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="3"/>
-        <v>53.715968621843999</v>
+        <v>116.90804435771062</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1656,11 +1656,11 @@
       </c>
       <c r="B93">
         <f t="shared" ca="1" si="2"/>
-        <v>74.099538965711773</v>
+        <v>82.804163756822817</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="3"/>
-        <v>47.543872393186255</v>
+        <v>122.68370285957216</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,11 +1669,11 @@
       </c>
       <c r="B94">
         <f t="shared" ca="1" si="2"/>
-        <v>83.21903915782076</v>
+        <v>76.7492523727188</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="3"/>
-        <v>45.128213044198723</v>
+        <v>118.58318034356125</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -1682,11 +1682,11 @@
       </c>
       <c r="B95">
         <f t="shared" ca="1" si="2"/>
-        <v>83.33582454825833</v>
+        <v>84.673386303998655</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="3"/>
-        <v>48.051943773209914</v>
+        <v>121.12955030735739</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -1695,11 +1695,11 @@
       </c>
       <c r="B96">
         <f t="shared" ca="1" si="2"/>
-        <v>80.798854312512049</v>
+        <v>86.561665655519093</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="3"/>
-        <v>52.807966097344732</v>
+        <v>129.41124609461127</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="B97">
         <f t="shared" ca="1" si="2"/>
-        <v>76.002554359994292</v>
+        <v>80.922229325520689</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="3"/>
-        <v>45.162170823808836</v>
+        <v>125.86056323315167</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="B98">
         <f t="shared" ca="1" si="2"/>
-        <v>74.224813739862952</v>
+        <v>78.887431812070062</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="3"/>
-        <v>50.963154215717921</v>
+        <v>129.46592369487138</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="B99">
         <f t="shared" ca="1" si="2"/>
-        <v>82.509403813618533</v>
+        <v>80.587766859224502</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="3"/>
-        <v>49.14233728553446</v>
+        <v>124.14816055158991</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B100">
         <f t="shared" ca="1" si="2"/>
-        <v>79.5722510910024</v>
+        <v>84.659598096438117</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="3"/>
-        <v>49.724293221856087</v>
+        <v>126.49779587394977</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B101">
         <f t="shared" ca="1" si="2"/>
-        <v>77.723325684263173</v>
+        <v>81.500396533618172</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="3"/>
-        <v>51.790392776909222</v>
+        <v>134.99687989862031</v>
       </c>
     </row>
   </sheetData>
